--- a/Farmacias Particular e Rede Pública.xlsx
+++ b/Farmacias Particular e Rede Pública.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karinesouza\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD8CDDE-0EF2-42B8-9CA0-4B26B1CF5FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BC0DDE-40E7-4B5A-B2EA-FBAD92FCDEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{FCA29981-1892-4143-8D4D-656C33CF1167}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FCA29981-1892-4143-8D4D-656C33CF1167}"/>
   </bookViews>
   <sheets>
     <sheet name="Particular" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="171">
   <si>
     <t>Particular</t>
   </si>
@@ -537,6 +537,12 @@
   </si>
   <si>
     <t>Rede Pública</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/emZFKLAYQzCr9KYx8</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wCSHT4Qe3DbnQ3qm9</t>
   </si>
 </sst>
 </file>
@@ -833,6 +839,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -849,15 +864,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1187,13 +1193,13 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="20"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -1252,7 +1258,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>11</v>
+        <v>169</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>19</v>
@@ -1269,7 +1275,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>18</v>
@@ -1739,8 +1745,8 @@
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" tooltip="https://business.google.com/v/farma-med/011314754108339128777/4d11/_?caid=23642169785&amp;agid=197151861547&amp;gclid=eaiaiqobchmi0oupgdo-lwmv9lziab1bucdkebayasaaegieu_d_bwe&amp;gad_source=6&amp;gad_campaignid=23642169785&amp;gbraid=0aaaabdfgwxpgy1lwqifdk-af5lkat3oma" display="https://business.google.com/v/farma-med/011314754108339128777/4d11/_?caid=23642169785&amp;agid=197151861547&amp;gclid=EAIaIQobChMI0OuPgdO-lwMV9lZIAB1BuCDkEBAYASAAEgIEU_D_BwE&amp;gad_source=6&amp;gad_campaignid=23642169785&amp;gbraid=0AAAABDFGWXpgy1LWQifDk-af5LKAT3OMA" xr:uid="{F11F0E0E-4887-4D22-B4B7-52A0CE260FFD}"/>
     <hyperlink ref="D4" r:id="rId2" display="tel:0151153477245" xr:uid="{1F225218-1318-403F-9EB6-408BB58E5AD5}"/>
-    <hyperlink ref="C7" r:id="rId3" display="https://maps.google.com/maps?vet=10CAAQoqAOahcKEwiosv2J-sqXAxUAAAAAHQAAAAAQDA..i&amp;aep=42&amp;amc=1&amp;sca_esv=7e69963a3bb46de9&amp;udm&amp;fvr=1&amp;pvq=Cg0vZy8xMWM2enJoeWtxIhsKFWRyb2dhcmlhIHPDo28gcGF1bG9BdhACGAOJAfwDrtbuZVRT&amp;lqi=Cl5kcm9nYXJpYSBzw6NvIHBhdWxvQXYuIFlvamlybyBUYWthb2thLCA0NTI4IC0gQWxwaGF2aWxsZSwgU2FudGFuYSBkZSBQYXJuYcOtYmEgLSBTUCwgMDY1NDEtMDM4SLbs3-ubq4CACFpyEAAQARACGAAYARgDGAQYBhgHGAkYChgLGAwiVmRyb2dhcmlhIHPDo28gcGF1bG9hdiB5b2ppcm8gdGFrYW9rYSA0NTI4IGFscGhhdmlsbGUgc2FudGFuYSBkZSBwYXJuYcOtYmEgc3AgMDY1NDEgMDM4kgEJZHJ1Z3N0b3Jl&amp;cs=1&amp;um=1&amp;ie=UTF-8&amp;fb=1&amp;gl=br&amp;sa=X&amp;ftid=0x94cf0300e78c7ab7:0x535465eed6ae03fc" xr:uid="{53C412E8-FF9D-4B3D-8E3C-5EF87A2EB646}"/>
-    <hyperlink ref="C6" r:id="rId4" display="https://maps.google.com/maps?vet=10CAAQoqAOahcKEwiosv2J-sqXAxUAAAAAHQAAAAAQBQ..i&amp;aep=42&amp;amc=1&amp;sca_esv=7e69963a3bb46de9&amp;udm&amp;fvr=1&amp;pvq=Cg0vZy8xMXl4enAxMTV6IhsKFWRyb2dhcmlhIHPDo28gcGF1bG9BdhACGAOJAY5lMl2vHhmr&amp;lqi=Cl5kcm9nYXJpYSBzw6NvIHBhdWxvQXYuIFlvamlybyBUYWthb2thLCA0NTI4IC0gQWxwaGF2aWxsZSwgU2FudGFuYSBkZSBQYXJuYcOtYmEgLSBTUCwgMDY1NDEtMDM4SL6JwurzvYCACFp0EAAQARACGAAYARgDGAQYBRgGGAcYCRgKGAsYDCJWZHJvZ2FyaWEgc8OjbyBwYXVsb2F2IHlvamlybyB0YWthb2thIDQ1MjggYWxwaGF2aWxsZSBzYW50YW5hIGRlIHBhcm5hw61iYSBzcCAwNjU0MSAwMziSAQlkcnVnc3RvcmWaAURDaTlEUVVsUlFVTnZaRU5vZEhsalJqbHZUMnRLY21WR1FuVmlWMVpaVGpJNE1GVlZjSEZpUjFVeVVraG9kR014UlJBQvoBBAg8ECw&amp;cs=1&amp;um=1&amp;ie=UTF-8&amp;fb=1&amp;gl=br&amp;sa=X&amp;ftid=0x94cf030013c5e739:0xab191eaf5d32658e" xr:uid="{3E276343-C028-4F43-939E-E4FE0EF54EDD}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{53C412E8-FF9D-4B3D-8E3C-5EF87A2EB646}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{3E276343-C028-4F43-939E-E4FE0EF54EDD}"/>
     <hyperlink ref="C5" r:id="rId5" xr:uid="{A17EF509-53AD-4076-BB11-63A25EDA90B1}"/>
     <hyperlink ref="C8" r:id="rId6" xr:uid="{EFDBB0E0-B5B7-48A8-8F7F-4A8B8BFB16C5}"/>
     <hyperlink ref="D8" r:id="rId7" display="https://www.google.com/search?q=drogaria+s%C3%A3o+paulo+cajamar&amp;amc=1&amp;aep=42&amp;biw=638&amp;bih=944&amp;sca_esv=7e69963a3bb46de9&amp;sxsrf=APpeQnv8GRBtbrDIFeQ-WgdD7yLLYfBWmA%3A1792580531238&amp;ei=s5vYaoaADtXB5OUP5ePwyA4&amp;gs_ssp=eJzj4tVP1zc0TDJLTy4qNzY2YLRSNaiwNElOM0wxTDQ1T04zNTNOszKoMElLTEw2NE-2TDQ3trQ0S_OSTinKT08sykxUKD68OF-hILE0J18hOTErMTexCAAA2BqC&amp;oq=drogaria+s%C3%A3o+paulo+ca&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmRyb2dhcmlhIHPDo28gcGF1bG8gY2EqDggBGIAEGMcBGK8BGI4FMggQABiABBi0BzIOEC4YgAQYxwEYrwEYjgUyERAuGIAEGLQHGMcBGK8BGI4FMgUQABiABDIFEAAYgAQyBRAAGIAEMg4QLhiABBjHARivARiOBTIREC4YgAQYtAcYxwEYrwEYjgUyBRAAGIAEMggQABiABBi0B0jHDlCABFjNBXABeACQAQCYAYYBoAGCA6oBAzAuM7gBAcgBAPgBAZgCA6ACpQLCAgoQABhHGNYEGLADmAMAiAYBkAYIkgcDMS4yoAeNIbIHAzAuMrgHmwLCBwUyLTEuMsgHHoAIAQ&amp;sclient=gws-wiz-serp" xr:uid="{796EA8C7-AFAC-40C6-A422-158A1C5FEAFB}"/>
@@ -1826,24 +1832,24 @@
   <sheetData>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:4" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="20"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="23"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="17" t="s">
         <v>3</v>
       </c>
     </row>
